--- a/input/Domains/Game/GameMessageTable.xlsx
+++ b/input/Domains/Game/GameMessageTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3805BC42-6464-E342-8F4A-1511BD9C6AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84614757-9EB6-EA48-B153-90D2059E6AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1380" yWindow="500" windowWidth="37020" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
   <si>
     <t>messageId</t>
   </si>
@@ -155,6 +155,14 @@
   </si>
   <si>
     <t>BATTLE_PASS_005</t>
+  </si>
+  <si>
+    <t>msg_stage_max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAGE_CLEAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -538,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -707,10 +715,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
         <v>34</v>
@@ -718,10 +726,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
         <v>34</v>
@@ -729,10 +737,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
         <v>34</v>
@@ -740,10 +748,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
         <v>34</v>
@@ -751,12 +759,23 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
         <v>43</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>44</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>34</v>
       </c>
     </row>

--- a/input/Domains/Game/GameMessageTable.xlsx
+++ b/input/Domains/Game/GameMessageTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84614757-9EB6-EA48-B153-90D2059E6AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CB1DDE-3D6C-C94E-BDF3-4E9BB68B1479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="500" windowWidth="37020" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40280" yWindow="-1560" windowWidth="37020" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GAME_MESSAGE" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>messageId</t>
   </si>
@@ -52,37 +52,10 @@
     <t>NONE/SESSION_SUM/SESSION_MAX/SESSION_MIN/TOTAL_SUM/TOTAL_MAX/TOTAL_MIN</t>
   </si>
   <si>
-    <t>msg_achieve_001_sum</t>
-  </si>
-  <si>
     <t>ACHIEVE_001</t>
   </si>
   <si>
     <t>TOTAL_SUM</t>
-  </si>
-  <si>
-    <t>msg_achieve_002_sum</t>
-  </si>
-  <si>
-    <t>ACHIEVE_002</t>
-  </si>
-  <si>
-    <t>msg_achieve_003_sum</t>
-  </si>
-  <si>
-    <t>ACHIEVE_003</t>
-  </si>
-  <si>
-    <t>msg_achieve_004_sum</t>
-  </si>
-  <si>
-    <t>ACHIEVE_004</t>
-  </si>
-  <si>
-    <t>msg_achieve_005_sum</t>
-  </si>
-  <si>
-    <t>ACHIEVE_005</t>
   </si>
   <si>
     <t>msg_mission_clear_sum</t>
@@ -162,6 +135,10 @@
   </si>
   <si>
     <t>STAGE_CLEAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg_achieve_001_total</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -546,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -594,24 +571,24 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -622,7 +599,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -633,7 +610,7 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -644,7 +621,7 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -655,128 +632,84 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
       <c r="C17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/input/Domains/Game/GameMessageTable.xlsx
+++ b/input/Domains/Game/GameMessageTable.xlsx
@@ -1,170 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maoshy/Documents/Projects/devian/input/Domains/Game/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CB1DDE-3D6C-C94E-BDF3-4E9BB68B1479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40280" yWindow="-1560" windowWidth="37020" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="40280" yWindow="-1560" windowWidth="37020" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="GAME_MESSAGE" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GAME_MESSAGE" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
-  <si>
-    <t>messageId</t>
-  </si>
-  <si>
-    <t>messageType</t>
-  </si>
-  <si>
-    <t>saveType</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>GAME_MESSAGE_TYPE</t>
-  </si>
-  <si>
-    <t>GAME_MESSAGE_SAVE_TYPE</t>
-  </si>
-  <si>
-    <t>pk</t>
-  </si>
-  <si>
-    <t>내부 메시지 ID (정본)</t>
-  </si>
-  <si>
-    <t>메시지 타입</t>
-  </si>
-  <si>
-    <t>NONE/SESSION_SUM/SESSION_MAX/SESSION_MIN/TOTAL_SUM/TOTAL_MAX/TOTAL_MIN</t>
-  </si>
-  <si>
-    <t>ACHIEVE_001</t>
-  </si>
-  <si>
-    <t>TOTAL_SUM</t>
-  </si>
-  <si>
-    <t>msg_mission_clear_sum</t>
-  </si>
-  <si>
-    <t>MISSION_CLEAR</t>
-  </si>
-  <si>
-    <t>SESSION_SUM</t>
-  </si>
-  <si>
-    <t>msg_mission_001_sum</t>
-  </si>
-  <si>
-    <t>TEST_001</t>
-  </si>
-  <si>
-    <t>msg_mission_002_sum</t>
-  </si>
-  <si>
-    <t>TEST_002</t>
-  </si>
-  <si>
-    <t>msg_mission_003_sum</t>
-  </si>
-  <si>
-    <t>TEST_003</t>
-  </si>
-  <si>
-    <t>msg_mission_004_sum</t>
-  </si>
-  <si>
-    <t>TEST_004</t>
-  </si>
-  <si>
-    <t>msg_score_max</t>
-  </si>
-  <si>
-    <t>STAGE_SCORE</t>
-  </si>
-  <si>
-    <t>TOTAL_MAX</t>
-  </si>
-  <si>
-    <t>msg_battle_pass_001</t>
-  </si>
-  <si>
-    <t>BATTLE_PASS_001</t>
-  </si>
-  <si>
-    <t>msg_battle_pass_002</t>
-  </si>
-  <si>
-    <t>BATTLE_PASS_002</t>
-  </si>
-  <si>
-    <t>msg_battle_pass_003</t>
-  </si>
-  <si>
-    <t>BATTLE_PASS_003</t>
-  </si>
-  <si>
-    <t>msg_battle_pass_004</t>
-  </si>
-  <si>
-    <t>BATTLE_PASS_004</t>
-  </si>
-  <si>
-    <t>msg_battle_pass_005</t>
-  </si>
-  <si>
-    <t>BATTLE_PASS_005</t>
-  </si>
-  <si>
-    <t>msg_stage_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STAGE_CLEAR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>msg_achieve_001_total</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -183,21 +53,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -522,198 +451,299 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col width="20.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="19.5703125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="23.85546875" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>message_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>message_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>save_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GAME_MESSAGE_TYPE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GAME_MESSAGE_SAVE_TYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pk</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>내부 메시지 ID (정본)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>메시지 타입</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NONE/SESSION_SUM/SESSION_MAX/SESSION_MIN/TOTAL_SUM/TOTAL_MAX/TOTAL_MIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>msg_achieve_001_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ACHIEVE_001</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TOTAL_SUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>msg_mission_clear_sum</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MISSION_CLEAR</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SESSION_SUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>msg_mission_001_sum</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TEST_001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SESSION_SUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>msg_mission_002_sum</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TEST_002</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SESSION_SUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>msg_mission_003_sum</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TEST_003</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SESSION_SUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>msg_mission_004_sum</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TEST_004</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SESSION_SUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>msg_score_max</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>STAGE_SCORE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TOTAL_MAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>msg_stage_max</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>STAGE_CLEAR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TOTAL_MAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>msg_battle_pass_001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BATTLE_PASS_001</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TOTAL_MAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>msg_battle_pass_002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BATTLE_PASS_002</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TOTAL_MAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>msg_battle_pass_003</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BATTLE_PASS_003</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TOTAL_MAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>msg_battle_pass_004</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BATTLE_PASS_004</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TOTAL_MAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>msg_battle_pass_005</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BATTLE_PASS_005</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TOTAL_MAX</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>